--- a/src/tests/data/output/tuc_17_1_ieee14.xlsx
+++ b/src/tests/data/output/tuc_17_1_ieee14.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
